--- a/offers/seasonal/عروض اليوم الوطني سنترم ولاكتونيك.xlsx
+++ b/offers/seasonal/عروض اليوم الوطني سنترم ولاكتونيك.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YAHAY ZAQZOUQ\IMPORTANT\ملفات العروض\9\عروض اليوم الوطني\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YAHAY ZAQZOUQ\IMPORTANT\ملفات العروض\9\عروض اليوم الوطني\Github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F73FD9-5D7E-4390-8FF9-AEE1EFE8A588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81C3150-4BFA-4F95-98AC-76C20307F5D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="30">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -49,121 +49,61 @@
     <t>خصم</t>
   </si>
   <si>
-    <t>00042954</t>
-  </si>
-  <si>
     <t>CENTRUM 1008SILVER ADUL50+ 30TAB</t>
   </si>
   <si>
-    <t>00044352</t>
-  </si>
-  <si>
     <t>CENTRUM ADULT F.SUPPLE 30TAB 74351</t>
   </si>
   <si>
-    <t>00042953</t>
-  </si>
-  <si>
     <t>CENTRUM ADULTS 100 TAB 995</t>
   </si>
   <si>
-    <t>00042952</t>
-  </si>
-  <si>
     <t>CENTRUM SILVER ADU50+ 100 TAB 1015</t>
   </si>
   <si>
-    <t>00012989</t>
-  </si>
-  <si>
     <t>لاكتونيك 350 جم (LF)</t>
   </si>
   <si>
-    <t>00012988</t>
-  </si>
-  <si>
     <t>لاكتونيك 400 جم (AR)</t>
   </si>
   <si>
-    <t>00020383</t>
-  </si>
-  <si>
     <t>لاكتونيك اتش ايه بلس (1)400 جم</t>
   </si>
   <si>
-    <t>00020384</t>
-  </si>
-  <si>
     <t>لاكتونيك اتش ايه بلس (2)400 جم</t>
   </si>
   <si>
-    <t>00019333</t>
-  </si>
-  <si>
     <t>لاكتونيك اييز 2 جو رقم (1) 800 جم</t>
   </si>
   <si>
-    <t>00019334</t>
-  </si>
-  <si>
     <t>لاكتونيك اييز 2 جو رقم (2) 800 جم</t>
   </si>
   <si>
-    <t>00040360</t>
-  </si>
-  <si>
     <t>لاكتونيك اييز 2 جو رقم (3) 1200 جم</t>
   </si>
   <si>
-    <t>00018200</t>
-  </si>
-  <si>
     <t>لاكتونيك اييز 2 جو رقم (3) 400 جم</t>
   </si>
   <si>
-    <t>00019335</t>
-  </si>
-  <si>
     <t>لاكتونيك اييز 2 جو رقم (3) 800 جم</t>
   </si>
   <si>
-    <t>0003039</t>
-  </si>
-  <si>
     <t>لاكتونيك رقم (1) 400 جم</t>
   </si>
   <si>
-    <t>00013576</t>
-  </si>
-  <si>
     <t>لاكتونيك رقم (1) 800 جرام</t>
   </si>
   <si>
-    <t>0003040</t>
-  </si>
-  <si>
     <t>لاكتونيك رقم (2) 400 جم</t>
   </si>
   <si>
-    <t>00012975</t>
-  </si>
-  <si>
     <t>لاكتونيك رقم (2) 800 جرام</t>
   </si>
   <si>
-    <t>00040359</t>
-  </si>
-  <si>
     <t>لاكتونيك رقم (3) 1200 جرام</t>
   </si>
   <si>
-    <t>0003041</t>
-  </si>
-  <si>
     <t>لاكتونيك رقم (3) 400 جرام</t>
-  </si>
-  <si>
-    <t>00012991</t>
   </si>
   <si>
     <t>لاكتونيك رقم (3) 800 جرام</t>
@@ -234,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -253,6 +193,7 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -628,11 +569,11 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="8">
+        <v>42954</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="C2" s="3">
         <v>32.89</v>
@@ -651,11 +592,11 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
+      <c r="A3" s="8">
+        <v>44352</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3">
         <v>32.89</v>
@@ -674,11 +615,11 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
+      <c r="A4" s="8">
+        <v>42953</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3">
         <v>97.75</v>
@@ -697,11 +638,11 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
+      <c r="A5" s="8">
+        <v>42952</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3">
         <v>97.75</v>
@@ -720,17 +661,17 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
+      <c r="A6" s="8">
+        <v>12989</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3">
         <v>46</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E6" s="4">
         <v>46277</v>
@@ -743,17 +684,17 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>19</v>
+      <c r="A7" s="8">
+        <v>12988</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3">
         <v>46</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E7" s="4">
         <v>46277</v>
@@ -766,17 +707,17 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
+      <c r="A8" s="8">
+        <v>20383</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3">
         <v>56.35</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E8" s="4">
         <v>46277</v>
@@ -789,17 +730,17 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
+      <c r="A9" s="8">
+        <v>20384</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3">
         <v>56.35</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E9" s="4">
         <v>46277</v>
@@ -812,17 +753,17 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>25</v>
+      <c r="A10" s="8">
+        <v>19333</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3">
         <v>94.79</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E10" s="4">
         <v>46277</v>
@@ -835,17 +776,17 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>27</v>
+      <c r="A11" s="8">
+        <v>19334</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C11" s="3">
         <v>94.79</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E11" s="4">
         <v>46277</v>
@@ -858,17 +799,17 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>29</v>
+      <c r="A12" s="8">
+        <v>40360</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C12" s="3">
         <v>125.42</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E12" s="4">
         <v>46277</v>
@@ -881,17 +822,17 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>31</v>
+      <c r="A13" s="8">
+        <v>18200</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3">
         <v>47.81</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E13" s="4">
         <v>46277</v>
@@ -904,17 +845,17 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>33</v>
+      <c r="A14" s="8">
+        <v>19335</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C14" s="3">
         <v>94.79</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E14" s="4">
         <v>46277</v>
@@ -927,17 +868,17 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>35</v>
+      <c r="A15" s="8">
+        <v>3039</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3">
         <v>40.799999999999997</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E15" s="4">
         <v>46277</v>
@@ -950,17 +891,17 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>37</v>
+      <c r="A16" s="8">
+        <v>13576</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C16" s="3">
         <v>80.8</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E16" s="4">
         <v>46277</v>
@@ -973,17 +914,17 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>39</v>
+      <c r="A17" s="8">
+        <v>3040</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C17" s="3">
         <v>40.799999999999997</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E17" s="4">
         <v>46277</v>
@@ -996,17 +937,17 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>41</v>
+      <c r="A18" s="8">
+        <v>12975</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C18" s="3">
         <v>80.8</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E18" s="4">
         <v>46277</v>
@@ -1019,17 +960,17 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>43</v>
+      <c r="A19" s="8">
+        <v>40359</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C19" s="3">
         <v>110.4</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E19" s="4">
         <v>46277</v>
@@ -1042,17 +983,17 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>45</v>
+      <c r="A20" s="8">
+        <v>3041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C20" s="3">
         <v>40.799999999999997</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E20" s="4">
         <v>46277</v>
@@ -1065,17 +1006,17 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>47</v>
+      <c r="A21" s="8">
+        <v>12991</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C21" s="3">
         <v>80.8</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E21" s="4">
         <v>46277</v>
